--- a/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI (SDIT) BULAN 09 TAHUN 2026.xlsx
+++ b/public/upload/report/REKAP TOTAL NILAI KPI YAYASAN PENDIDIKAN ALQALAM KENDARI (SDIT) BULAN 09 TAHUN 2026.xlsx
@@ -754,14 +754,14 @@
         <v>17</v>
       </c>
       <c r="C6" s="3">
-        <v>7.0</v>
+        <v>13.0</v>
       </c>
       <c r="D6" s="3">
-        <v>23.6</v>
+        <v>16.68</v>
       </c>
       <c r="E6" s="3">
         <f>AVERAGE(C6:D6)</f>
-        <v>15.3</v>
+        <v>14.84</v>
       </c>
       <c r="F6" s="3" t="str">
         <f>IF(E6&gt;=90,"Sangat Baik",IF(E6&gt;=80,"Baik",IF(E6&gt;=70,"Cukup",IF(E6&gt;=60,"Kurang","Perlu Pembinaan"))))</f>
@@ -779,20 +779,20 @@
         <v>60000</v>
       </c>
       <c r="J6" s="4">
-        <v>20000.0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
-        <v>10000.0</v>
+        <v>0</v>
       </c>
       <c r="L6" s="4">
-        <v>10000.0</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4">
-        <v>20000.0</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4">
         <f>SUM(I6:M6)</f>
-        <v>120000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -803,14 +803,14 @@
         <v>18</v>
       </c>
       <c r="C7" s="3">
-        <v>12.0</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
-        <v>35.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <f>AVERAGE(C7:D7)</f>
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="str">
         <f>IF(E7&gt;=90,"Sangat Baik",IF(E7&gt;=80,"Baik",IF(E7&gt;=70,"Cukup",IF(E7&gt;=60,"Kurang","Perlu Pembinaan"))))</f>
